--- a/exports/xlsx/MaternaLink_Pricing_Calculator.xlsx
+++ b/exports/xlsx/MaternaLink_Pricing_Calculator.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK Calculator" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Calculator" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price Book" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Packages" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -101,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,16 +113,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B10:H26"/>
+  <dimension ref="B10:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -534,7 +536,7 @@
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Working calculators for UK services and programme deployments, plus the published price book. Yellow cells are inputs. Every price is an ESTIMATE until validated with three buyers per segment.</t>
+          <t>Three tiers across nine modules. Yellow cells are inputs you can change. Two modules are marked as not sellable until they hold a medical device licence. Every price is an ESTIMATE until tested with three buyers per segment.</t>
         </is>
       </c>
     </row>
@@ -591,7 +593,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Trust or hospital pricing by module and service plan</t>
+          <t>A UK hospital, tier by tier, with cost to serve and margin</t>
         </is>
       </c>
     </row>
@@ -603,7 +605,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Per-woman tiered pricing for state and NGO programmes</t>
+          <t>An African state or NGO programme, tiered by volume</t>
         </is>
       </c>
     </row>
@@ -615,12 +617,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Published ranges per product</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="6" t="inlineStr">
+          <t>Every module, both markets, and whether you can sell it yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>The three packages to offer, and the rules you do not break</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Colour code: yellow cells are inputs you can change; blue headers are fixed; every figure is an ESTIMATE unless labelled VERIFIED (see FACTS_BASE).</t>
         </is>
@@ -641,26 +655,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>MATERNALINK PRICING CALCULATOR — UK (all inputs are ESTIMATES to validate)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
+          <t>MATERNALINK PRICING CALCULATOR — UK HOSPITAL (change the yellow cells)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>TIER 1 — every pregnant woman</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -677,7 +690,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Annual births at the service</t>
+          <t>Births / women enrolled per year</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
@@ -685,182 +698,168 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Drives site-licence band</t>
+          <t>Drives the site-licence band</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Women enrolled per year</t>
+          <t>Tier 1 price per woman per year (£)</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>5000</v>
+        <v>22</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Usually equals births for Core</t>
+          <t>Range 16-30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Core price per woman (£)</t>
+          <t>Site licence (£)</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>22</v>
+        <v>20000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Range 18–36</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Site licence (£)</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>12k–30k by births band</t>
+          <t>12k-30k by births</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Engagement module: enrolled women</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>TIER 2 — women watched on a device</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engagement price per woman (£)</t>
+          <t>Monitored women per year</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>10</v>
+        <v>800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Range 8–14</t>
+          <t>Typically 15-25% of births</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Triage module sites</t>
+          <t>Price per monitored woman per MONTH (£)</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Range 22-38</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Triage price per site (£)</t>
+          <t>Average months monitored</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>25000</v>
+        <v>4.2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15k–35k</t>
+          <t>16-22 weeks</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Glucose module: women with condition</t>
+          <t>Devices in rotation</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Typically 5–10% of cohort</t>
+          <t>Fewer than monitored women; they rotate</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Glucose price per woman (£)</t>
+          <t>Device lease charged per month (£)</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20–30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Watch devices leased</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Range 4.50-7.00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Watch lease per device per month (£)</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4–7</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>TIER 3 — the institution</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics (£ per site)</t>
+          <t>Hospital dashboard (£/year)</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>8000</v>
+        <v>28000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6k–12k</t>
+          <t>18k-40k by births</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Integration interfaces (count)</t>
+          <t>Integration interfaces</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
@@ -871,7 +870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Integration setup per interface (£)</t>
+          <t>Integration setup each (£)</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
@@ -879,14 +878,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15k–40k</t>
+          <t>15k-40k, one-off</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Integration annual per interface (£)</t>
+          <t>Integration annual each (£)</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
@@ -894,216 +893,381 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4k–8k</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Implementation one-off (£)</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>45000</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>25k–75k</t>
+          <t>4k-8k</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Service plan % (Standard 0.20 / Enhanced 0.26 / Premium 0.32)</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>ADD-ON MODULES</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Newborn module per birth (£)</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8-14. Excludes jaundice imaging</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Outputs</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Voice diary per woman per year (£)</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3-5 once built</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Core software</t>
-        </is>
-      </c>
-      <c r="B24" s="11">
-        <f>B4*0+B5*B6+B7</f>
-        <v/>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Glucose: women with the condition</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>About 5-10% of the cohort</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="B25" s="11">
-        <f>B8*B9</f>
-        <v/>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Glucose price each per year (£)</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20-30, after a regulatory opinion</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Triage</t>
-        </is>
-      </c>
-      <c r="B26" s="11">
-        <f>B10*B11</f>
-        <v/>
-      </c>
-      <c r="C26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Glucose</t>
-        </is>
-      </c>
-      <c r="B27" s="11">
-        <f>B12*B13</f>
-        <v/>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>AI engine uplift on Tier 2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.25-0.35 ONLY after certification</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Analytics</t>
-        </is>
-      </c>
-      <c r="B28" s="11">
-        <f>B16</f>
-        <v/>
-      </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>SERVICE AND SETUP</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software subtotal (annual)</t>
-        </is>
-      </c>
-      <c r="B29" s="11">
-        <f>SUM(B24:B28)</f>
-        <v/>
+          <t>Service plan (0.20 Std / 0.26 Enh / 0.32 Prem)</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>0.26</v>
       </c>
       <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Annual service plan</t>
-        </is>
-      </c>
-      <c r="B30" s="11">
-        <f>B29*B21</f>
-        <v/>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>Implementation one-off (£)</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>25k-75k</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Watch lease (annual)</t>
-        </is>
-      </c>
-      <c r="B31" s="11">
-        <f>B14*B15*12</f>
-        <v/>
-      </c>
-      <c r="C31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Integration annual</t>
-        </is>
-      </c>
-      <c r="B32" s="11">
-        <f>B17*B19</f>
-        <v/>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Cost to serve one monitored woman per month (£)</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ESTIMATE — your developer must confirm</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Recurring annual total</t>
-        </is>
-      </c>
-      <c r="B33" s="11">
-        <f>B29+B30+B31+B32</f>
-        <v/>
-      </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>OUTPUTS</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>One-off: integration setup + implementation</t>
+          <t>Tier 1 revenue</t>
         </is>
       </c>
       <c r="B34" s="11">
-        <f>B17*B18+B20</f>
-        <v/>
-      </c>
-      <c r="C34" t="inlineStr"/>
+        <f>B4*B5+B6</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Tier 2 revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="11">
+        <f>B9*B10*B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI engine uplift</t>
+        </is>
+      </c>
+      <c r="B36" s="11">
+        <f>B35*B26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Newborn module</t>
+        </is>
+      </c>
+      <c r="B37" s="11">
+        <f>B4*B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Voice diary</t>
+        </is>
+      </c>
+      <c r="B38" s="11">
+        <f>B4*B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Glucose module</t>
+        </is>
+      </c>
+      <c r="B39" s="11">
+        <f>B24*B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hospital dashboard</t>
+        </is>
+      </c>
+      <c r="B40" s="11">
+        <f>B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Integration, annual</t>
+        </is>
+      </c>
+      <c r="B41" s="11">
+        <f>B17*B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>SOFTWARE SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B42" s="12">
+        <f>SUM(B34:B41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Service plan</t>
+        </is>
+      </c>
+      <c r="B43" s="11">
+        <f>B42*B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Device leases (annual)</t>
+        </is>
+      </c>
+      <c r="B44" s="11">
+        <f>B12*B13*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>RECURRING ANNUAL TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="12">
+        <f>B42+B43+B44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>One-off: implementation + integration build</t>
+        </is>
+      </c>
+      <c r="B46" s="11">
+        <f>B30+B17*B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>YEAR 1 TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="12">
-        <f>B33+B34</f>
-        <v/>
-      </c>
-      <c r="C35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>YEAR 2+ RUN-RATE</t>
-        </is>
-      </c>
-      <c r="B36" s="12">
-        <f>B33</f>
-        <v/>
-      </c>
-      <c r="C36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Recurring cost per enrolled woman (£)</t>
-        </is>
-      </c>
-      <c r="B37" s="13">
-        <f>IF(B5&gt;0,B33/B5,0)</f>
-        <v/>
-      </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="B47" s="12">
+        <f>B45+B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>YEAR 2+ RUN RATE</t>
+        </is>
+      </c>
+      <c r="B48" s="12">
+        <f>B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Year 1 revenue per birth (£)</t>
+        </is>
+      </c>
+      <c r="B49" s="13">
+        <f>IF(B4&gt;0,B47/B4,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Run-rate revenue per birth (£)</t>
+        </is>
+      </c>
+      <c r="B50" s="13">
+        <f>IF(B4&gt;0,B45/B4,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Your cost to serve the monitored women</t>
+        </is>
+      </c>
+      <c r="B51" s="11">
+        <f>B9*B11*B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Gross margin on Tier 2</t>
+        </is>
+      </c>
+      <c r="B52" s="14">
+        <f>IF(B35&gt;0,(B35-B51)/B35,0)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1116,26 +1280,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>MATERNALINK PRICING CALCULATOR — PROGRAMME (Africa / donor-funded)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
+          <t>MATERNALINK PRICING CALCULATOR — AFRICAN PROGRAMME</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>TIER 1 — every woman</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -1152,259 +1315,387 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Women enrolled</t>
+          <t>Women enrolled per year</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>15000</v>
+        <v>100000</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Core price per woman (£) — tiered: 10 / 7 / 5 / 4</t>
-        </is>
-      </c>
-      <c r="B5" s="14">
-        <f>IF(B4&lt;=5000,10,IF(B4&lt;=25000,7,IF(B4&lt;=100000,5,4)))</f>
+          <t>Tier 1 price per woman (£)</t>
+        </is>
+      </c>
+      <c r="B5" s="15">
+        <f>IF(B4&lt;=5000,9,IF(B4&lt;=25000,7,IF(B4&lt;=100000,5,4)))</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Formula applies the published tiers</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Engagement price per woman (£)</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3–5</t>
+          <t>Formula applies the published volume tiers</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Facilities with triage</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>TIER 2 — monitored women</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Triage per facility (£)</t>
+          <t>Monitored women</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>2500</v>
+        <v>15000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.5k–4k</t>
+          <t>About 15% of the cohort</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Training cohorts</t>
+          <t>Price per monitored woman per month (£)</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Range 3-6</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Training per cohort (£)</t>
+          <t>Average months monitored</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1.2k–2.5k</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Implementation one-off (£)</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>40k–120k</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Service plan % (0.20 / 0.28 / 0.35)</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>MODULES AND INSTITUTION</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Newborn module per birth (£)</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.50-3.00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Outputs</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Government / regional dashboard (£)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>60k-250k by population</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="B15" s="11">
-        <f>B4*B5</f>
-        <v/>
+          <t>Facilities with triage</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="B16" s="11">
-        <f>B4*B6</f>
-        <v/>
+          <t>Triage per facility (£)</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>2500</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Triage</t>
-        </is>
-      </c>
-      <c r="B17" s="11">
-        <f>B7*B8</f>
-        <v/>
-      </c>
-      <c r="C17" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software subtotal</t>
-        </is>
-      </c>
-      <c r="B18" s="11">
-        <f>SUM(B15:B17)</f>
-        <v/>
-      </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>SERVICE AND SETUP</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Service plan</t>
-        </is>
-      </c>
-      <c r="B19" s="11">
-        <f>MAX(B18*B12,12000)</f>
-        <v/>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Minimum £12,000</t>
-        </is>
-      </c>
+          <t>Service plan (0.20 / 0.28 / 0.35)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Training cohorts</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Training per cohort (£)</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Implementation one-off (£)</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>40k-200k by size</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>OUTPUTS</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tier 1 revenue</t>
+        </is>
+      </c>
+      <c r="B25" s="11">
+        <f>B4*B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tier 2 revenue</t>
+        </is>
+      </c>
+      <c r="B26" s="11">
+        <f>B8*B9*B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Newborn module</t>
+        </is>
+      </c>
+      <c r="B27" s="11">
+        <f>B4*B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Government dashboard</t>
+        </is>
+      </c>
+      <c r="B28" s="11">
+        <f>B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="B29" s="11">
+        <f>B15*B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>SOFTWARE SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B30" s="12">
+        <f>SUM(B25:B29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Service plan</t>
+        </is>
+      </c>
+      <c r="B31" s="11">
+        <f>MAX(B30*B19,12000)</f>
+        <v/>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Minimum £12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B20" s="11">
-        <f>B9*B10</f>
-        <v/>
-      </c>
-      <c r="C20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="B32" s="11">
+        <f>B20*B21</f>
+        <v/>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Recurs: new staff every year</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>RECURRING ANNUAL TOTAL</t>
+        </is>
+      </c>
+      <c r="B33" s="12">
+        <f>B30+B31+B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>YEAR 1 TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="12">
-        <f>B18+B19+B20+B11</f>
-        <v/>
-      </c>
-      <c r="C21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>YEAR 2+ RUN-RATE</t>
-        </is>
-      </c>
-      <c r="B22" s="12">
-        <f>B18+B19</f>
-        <v/>
-      </c>
-      <c r="C22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Year-1 cost per woman (£)</t>
-        </is>
-      </c>
-      <c r="B23" s="15">
-        <f>IF(B4&gt;0,B21/B4,0)</f>
-        <v/>
-      </c>
-      <c r="C23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="B34" s="12">
+        <f>B33+B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>YEAR 2+ RUN RATE</t>
+        </is>
+      </c>
+      <c r="B35" s="12">
+        <f>B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Year 1 cost per woman (£)</t>
+        </is>
+      </c>
+      <c r="B36" s="13">
+        <f>IF(B4&gt;0,B34/B4,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Run-rate cost per woman (£)</t>
         </is>
       </c>
-      <c r="B24" s="15">
-        <f>IF(B4&gt;0,B22/B4,0)</f>
-        <v/>
-      </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="B37" s="13">
+        <f>IF(B4&gt;0,B35/B4,0)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1417,364 +1708,626 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>UK model</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>UK indicative</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>Programme model</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>Programme indicative</t>
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Tier / module</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>What it covers</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>UK price</t>
+        </is>
+      </c>
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>Programme price</t>
+        </is>
+      </c>
+      <c r="E1" s="16" t="inlineStr">
+        <is>
+          <t>Sell it yet?</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>TIER 1 — everyone</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Site licence + per woman/yr</t>
+          <t>App, appointments, education, symptoms, mood, fetal movement log</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£12k–£30k + £18–£36</t>
+          <t>£16-30 per woman per year + £12k-30k site licence</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Per woman/yr tiered</t>
+          <t>£4-9 per woman per year</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10 / £7 / £5 / £4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engagement module</t>
+          <t>TIER 2 — watched closely</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Per woman/yr</t>
+          <t>Connected BP monitor, active surveillance, escalation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£8–£14</t>
+          <t>£22-38 per woman per MONTH</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Per woman/yr</t>
+          <t>£3-6 per woman per month</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£3–£5</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maternity triage</t>
+          <t>TIER 3 — hospital dashboard</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Per site/yr</t>
+          <t>Population view, response times, analytics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15k–£35k</t>
+          <t>£18k-40k per site per year</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Per facility/yr</t>
+          <t>Included in programme</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£1.5k–£4k</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Diabetes glucose diary</t>
+          <t>TIER 3 — government dashboard</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Per woman with condition/yr</t>
+          <t>Regional and national intelligence, de-identified data</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£20–£30</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Per woman</t>
+          <t>£60k-250k per year</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£6–£10</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Voice diaries</t>
+          <t>Clinician dashboard</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Per woman/yr</t>
+          <t>Patient list, red/amber/green, graphs, timeline, escalation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£3–£5</t>
+          <t>Included in Tiers 1 and 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Per woman</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£1–£2</t>
+          <t>Yes, if the rules belong to the hospital</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Maternity Watch (certified third-party device)</t>
+          <t>Newborn module</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lease per device/month</t>
+          <t>Feeding, temperature, breathing, observations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£4–£7 (or £120–£220 + £30/yr)</t>
+          <t>£8-14 per birth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lease per device/month</t>
+          <t>£1.50-3 per birth</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£2–£4 (or £90–£160 + £15/yr)</t>
+          <t>Yes, without jaundice imaging</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Integration pack</t>
+          <t>Voice diary</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Setup + annual per interface</t>
+          <t>Storage and playback only, no analysis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£15k–£40k + £4k–£8k</t>
+          <t>£3-5 per woman per year</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Setup + annual</t>
+          <t>£1-2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£8k–£25k + £3k</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Glucose diary</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Per site/yr</t>
+          <t>Self-reported readings against clinician targets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£6k–£12k</t>
+          <t>£20-30 per woman with the condition</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Included in programme</t>
+          <t>£6-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>After a regulatory opinion</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Per cohort of 25</t>
+          <t>EPR/FHIR, secure API, access control, audit trail</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£2.5k–£4.5k</t>
+          <t>£15k-40k setup + £4k-8k a year</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Per cohort of 30</t>
+          <t>£8k-25k + £3k</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£1.2k–£2.5k</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>AI ENGINE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>One-off per site</t>
+          <t>Maternal Instability Score, risk stratification, deterioration detection</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25k–£75k</t>
+          <t>Add 25-35% to Tier 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>One-off per programme</t>
+          <t>Add 20%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£40k–£120k</t>
+          <t>NO — needs a medical device licence</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pilot (12 weeks)</t>
+          <t>Jaundice photo screening</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Image-assisted newborn screening</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£40k–£90k</t>
+          <t>Not priced</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Not priced</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>On scope</t>
+          <t>NO — a device, and heavily patented already</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Service plans</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>% of licence</t>
+          <t>Validated BP monitor, thermometer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Std 18–22% · Enh 25–28% · Prem 30–35% (min £8k)</t>
+          <t>Lease £4.50-7 per month, or cost + 15%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>% of software</t>
+          <t>Lease £2-4 per month</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20% · 28% · 35% (min £12k)</t>
+          <t>Yes, resell certified kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Setup, configuration, training, safety paperwork</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£25k-75k per site</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>£40k-200k per programme</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Service plan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Support, releases, patching, safety maintenance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20% / 26% / 32% of licence</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20% / 28% / 35%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12 weeks, one site, evaluation report</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£40k-90k</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>On scope</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>What is in it</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>5,000-birth hospital, year 1</t>
+        </is>
+      </c>
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>Run rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tier 1 for all, Tier 2 for 500 women, clinician dashboard, service plan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>About £250,000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>About £205,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Essential plus hospital dashboard, newborn module, one integration</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>About £390,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>About £320,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Full ecosystem</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Complete plus 1,000 monitored, voice diary, glucose, premium support</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>About £490,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>About £410,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pilot first</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12 weeks fixed price, half the fee credited against year one</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Minimum contract</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£40,000 in the UK, £25,000 for a programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>No discounting below the floor</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Remove modules instead of cutting the price</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Devices always separate</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Never inside the software price</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Nothing unlicensed on a price list</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The AI engine and jaundice imaging stay off until certified</t>
         </is>
       </c>
     </row>
